--- a/data/IR_CHG_MPOFull.xlsx
+++ b/data/IR_CHG_MPOFull.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Образование\Магистратура\Диплом\ITMO_NIR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A45232DD-9B02-4ADB-820F-6A73E619A9AD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F00023C-B177-4423-91DA-1B7468EFDFCC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14775" yWindow="6735" windowWidth="21600" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="таб_дни изменений_полная версия" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6974" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6879" uniqueCount="167">
   <si>
     <t>Дата</t>
   </si>
@@ -738,7 +738,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -748,6 +748,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,7 +853,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -922,10 +928,25 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -943,20 +964,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1273,112 +1282,112 @@
       <c r="D2" s="17"/>
     </row>
     <row r="3" spans="1:65" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="43" t="s">
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="46"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="44" t="s">
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="43" t="s">
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="36" t="s">
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="AF3" s="37"/>
-      <c r="AG3" s="45" t="s">
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="AH3" s="36" t="s">
+      <c r="AH3" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="47"/>
-      <c r="AK3" s="47"/>
-      <c r="AL3" s="47"/>
-      <c r="AM3" s="36" t="s">
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+      <c r="AK3" s="42"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="AN3" s="47"/>
-      <c r="AO3" s="47"/>
-      <c r="AP3" s="47"/>
-      <c r="AQ3" s="47"/>
-      <c r="AR3" s="37"/>
-      <c r="AS3" s="36" t="s">
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="42"/>
+      <c r="AP3" s="42"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="AT3" s="47"/>
-      <c r="AU3" s="47"/>
-      <c r="AV3" s="47"/>
-      <c r="AW3" s="47"/>
-      <c r="AX3" s="47"/>
-      <c r="AY3" s="37"/>
-      <c r="AZ3" s="44" t="s">
+      <c r="AT3" s="42"/>
+      <c r="AU3" s="42"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="BA3" s="44"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="43"/>
-      <c r="BD3" s="36" t="s">
+      <c r="BA3" s="36"/>
+      <c r="BB3" s="36"/>
+      <c r="BC3" s="37"/>
+      <c r="BD3" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="BE3" s="47"/>
-      <c r="BF3" s="47"/>
-      <c r="BG3" s="47"/>
-      <c r="BH3" s="37"/>
-      <c r="BI3" s="36" t="s">
+      <c r="BE3" s="42"/>
+      <c r="BF3" s="42"/>
+      <c r="BG3" s="42"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="BJ3" s="37"/>
-      <c r="BK3" s="44" t="s">
+      <c r="BJ3" s="39"/>
+      <c r="BK3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="BL3" s="44" t="s">
+      <c r="BL3" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="BM3" s="44" t="s">
+      <c r="BM3" s="36" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:65" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1466,7 +1475,7 @@
       <c r="AF4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AG4" s="46"/>
+      <c r="AG4" s="41"/>
       <c r="AH4" s="1" t="s">
         <v>26</v>
       </c>
@@ -1554,16 +1563,17 @@
       <c r="BJ4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="BK4" s="43"/>
-      <c r="BL4" s="43"/>
-      <c r="BM4" s="43"/>
+      <c r="BK4" s="37"/>
+      <c r="BL4" s="37"/>
+      <c r="BM4" s="37"/>
     </row>
     <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>36739</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
+      <c r="B5" s="48">
+        <f t="shared" ref="B5:B68" si="0">BL5</f>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>44</v>
@@ -1756,8 +1766,9 @@
       <c r="A6" s="25">
         <v>36808</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>44</v>
+      <c r="B6" s="48">
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>44</v>
@@ -1953,8 +1964,9 @@
       <c r="A7" s="10">
         <v>36834</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
+      <c r="B7" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>44</v>
@@ -2150,8 +2162,9 @@
       <c r="A8" s="10">
         <v>36857</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>44</v>
+      <c r="B8" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>44</v>
@@ -2347,8 +2360,9 @@
       <c r="A9" s="10">
         <v>36906</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
+      <c r="B9" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>44</v>
@@ -2544,8 +2558,9 @@
       <c r="A10" s="10">
         <v>37063</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>44</v>
+      <c r="B10" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>44</v>
@@ -2741,8 +2756,9 @@
       <c r="A11" s="10">
         <v>37084</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>44</v>
+      <c r="B11" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>44</v>
@@ -2938,8 +2954,9 @@
       <c r="A12" s="25">
         <v>37133</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>44</v>
+      <c r="B12" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>44</v>
@@ -3135,8 +3152,9 @@
       <c r="A13" s="10">
         <v>37174</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
+      <c r="B13" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>44</v>
@@ -3332,8 +3350,9 @@
       <c r="A14" s="10">
         <v>37228</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>44</v>
+      <c r="B14" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>44</v>
@@ -3529,8 +3548,9 @@
       <c r="A15" s="10">
         <v>37236</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>44</v>
+      <c r="B15" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>44</v>
@@ -3726,8 +3746,9 @@
       <c r="A16" s="10">
         <v>37243</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>44</v>
+      <c r="B16" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>44</v>
@@ -3923,8 +3944,9 @@
       <c r="A17" s="10">
         <v>37265</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
+      <c r="B17" s="48">
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>44</v>
@@ -4120,8 +4142,9 @@
       <c r="A18" s="10">
         <v>37355</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>44</v>
+      <c r="B18" s="48">
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>44</v>
@@ -4317,8 +4340,9 @@
       <c r="A19" s="10">
         <v>37396</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>44</v>
+      <c r="B19" s="48">
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>44</v>
@@ -4514,8 +4538,9 @@
       <c r="A20" s="10">
         <v>37412</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>44</v>
+      <c r="B20" s="48">
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>44</v>
@@ -4711,8 +4736,9 @@
       <c r="A21" s="10">
         <v>37475</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>44</v>
+      <c r="B21" s="48">
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>44</v>
@@ -4908,8 +4934,9 @@
       <c r="A22" s="25">
         <v>37525</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>44</v>
+      <c r="B22" s="48">
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>44</v>
@@ -5105,8 +5132,9 @@
       <c r="A23" s="25">
         <v>37578</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>44</v>
+      <c r="B23" s="48">
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>44</v>
@@ -5302,8 +5330,9 @@
       <c r="A24" s="25">
         <v>37581</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>44</v>
+      <c r="B24" s="48">
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>44</v>
@@ -5499,8 +5528,9 @@
       <c r="A25" s="25">
         <v>37669</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>44</v>
+      <c r="B25" s="48">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>44</v>
@@ -5696,8 +5726,9 @@
       <c r="A26" s="25">
         <v>37687</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>44</v>
+      <c r="B26" s="48">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>44</v>
@@ -5893,8 +5924,9 @@
       <c r="A27" s="10">
         <v>37761</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
+      <c r="B27" s="48">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>44</v>
@@ -6090,8 +6122,9 @@
       <c r="A28" s="25">
         <v>37770</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>44</v>
+      <c r="B28" s="48">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>44</v>
@@ -6287,8 +6320,9 @@
       <c r="A29" s="10">
         <v>37774</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>44</v>
+      <c r="B29" s="48">
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>44</v>
@@ -6484,8 +6518,9 @@
       <c r="A30" s="10">
         <v>37793</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>44</v>
+      <c r="B30" s="48">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>44</v>
@@ -6681,8 +6716,9 @@
       <c r="A31" s="10">
         <v>37834</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>44</v>
+      <c r="B31" s="48">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>44</v>
@@ -6878,8 +6914,9 @@
       <c r="A32" s="25">
         <v>37908</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>44</v>
+      <c r="B32" s="48">
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>44</v>
@@ -7075,8 +7112,9 @@
       <c r="A33" s="10">
         <v>38001</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>44</v>
+      <c r="B33" s="48">
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>44</v>
@@ -7272,8 +7310,9 @@
       <c r="A34" s="25">
         <v>38022</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
+      <c r="B34" s="48">
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>44</v>
@@ -7469,8 +7508,9 @@
       <c r="A35" s="25">
         <v>38149</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>44</v>
+      <c r="B35" s="48">
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>44</v>
@@ -7666,8 +7706,9 @@
       <c r="A36" s="10">
         <v>38153</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>44</v>
+      <c r="B36" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>44</v>
@@ -7863,8 +7904,9 @@
       <c r="A37" s="25">
         <v>38453</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>44</v>
+      <c r="B37" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>44</v>
@@ -8060,8 +8102,9 @@
       <c r="A38" s="25">
         <v>38592</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>44</v>
+      <c r="B38" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>44</v>
@@ -8257,8 +8300,9 @@
       <c r="A39" s="10">
         <v>38712</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>44</v>
+      <c r="B39" s="48">
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>44</v>
@@ -8454,8 +8498,9 @@
       <c r="A40" s="10">
         <v>38782</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>44</v>
+      <c r="B40" s="48">
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>44</v>
@@ -8651,8 +8696,9 @@
       <c r="A41" s="10">
         <v>38817</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>44</v>
+      <c r="B41" s="48">
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>44</v>
@@ -8848,8 +8894,9 @@
       <c r="A42" s="10">
         <v>38894</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>44</v>
+      <c r="B42" s="48">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>44</v>
@@ -9047,8 +9094,9 @@
       <c r="A43" s="10">
         <v>38936</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>44</v>
+      <c r="B43" s="48">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>44</v>
@@ -9246,8 +9294,9 @@
       <c r="A44" s="10">
         <v>39013</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>44</v>
+      <c r="B44" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>44</v>
@@ -9443,8 +9492,9 @@
       <c r="A45" s="10">
         <v>39062</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>44</v>
+      <c r="B45" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>44</v>
@@ -9640,8 +9690,9 @@
       <c r="A46" s="10">
         <v>39111</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>44</v>
+      <c r="B46" s="48">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>44</v>
@@ -9837,8 +9888,9 @@
       <c r="A47" s="10">
         <v>39174</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>44</v>
+      <c r="B47" s="48">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>44</v>
@@ -10036,8 +10088,9 @@
       <c r="A48" s="10">
         <v>39252</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>44</v>
+      <c r="B48" s="48">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>44</v>
@@ -10233,8 +10286,9 @@
       <c r="A49" s="10">
         <v>39308</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>44</v>
+      <c r="B49" s="48">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>44</v>
@@ -10430,8 +10484,9 @@
       <c r="A50" s="10">
         <v>39366</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>44</v>
+      <c r="B50" s="48">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>44</v>
@@ -10627,8 +10682,9 @@
       <c r="A51" s="25">
         <v>39414</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>44</v>
+      <c r="B51" s="48">
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>44</v>
@@ -10824,8 +10880,9 @@
       <c r="A52" s="10">
         <v>39482</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>44</v>
+      <c r="B52" s="48">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>44</v>
@@ -11023,8 +11080,9 @@
       <c r="A53" s="25">
         <v>39509</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>44</v>
+      <c r="B53" s="48">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>44</v>
@@ -11220,8 +11278,9 @@
       <c r="A54" s="10">
         <v>39567</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>44</v>
+      <c r="B54" s="48">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>44</v>
@@ -11419,8 +11478,9 @@
       <c r="A55" s="10">
         <v>39609</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>44</v>
+      <c r="B55" s="48">
+        <f t="shared" si="0"/>
+        <v>10.75</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>44</v>
@@ -11616,8 +11676,9 @@
       <c r="A56" s="10">
         <v>39643</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>44</v>
+      <c r="B56" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>44</v>
@@ -11813,8 +11874,9 @@
       <c r="A57" s="10">
         <v>39709</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>44</v>
+      <c r="B57" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>44</v>
@@ -12010,8 +12072,9 @@
       <c r="A58" s="10">
         <v>39736</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>44</v>
+      <c r="B58" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>44</v>
@@ -12207,8 +12270,9 @@
       <c r="A59" s="25">
         <v>39741</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>44</v>
+      <c r="B59" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>44</v>
@@ -12404,8 +12468,9 @@
       <c r="A60" s="10">
         <v>39745</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>44</v>
+      <c r="B60" s="48">
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>44</v>
@@ -12601,8 +12666,9 @@
       <c r="A61" s="10">
         <v>39764</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>44</v>
+      <c r="B61" s="48">
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>44</v>
@@ -12798,8 +12864,9 @@
       <c r="A62" s="25">
         <v>39783</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>44</v>
+      <c r="B62" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>44</v>
@@ -12997,8 +13064,9 @@
       <c r="A63" s="25">
         <v>39793</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>44</v>
+      <c r="B63" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>44</v>
@@ -13194,8 +13262,9 @@
       <c r="A64" s="25">
         <v>39814</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>44</v>
+      <c r="B64" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>44</v>
@@ -13391,8 +13460,9 @@
       <c r="A65" s="25">
         <v>39833</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>44</v>
+      <c r="B65" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>44</v>
@@ -13588,8 +13658,9 @@
       <c r="A66" s="10">
         <v>39846</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>44</v>
+      <c r="B66" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>44</v>
@@ -13785,8 +13856,9 @@
       <c r="A67" s="10">
         <v>39854</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>44</v>
+      <c r="B67" s="48">
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>44</v>
@@ -13982,8 +14054,9 @@
       <c r="A68" s="10">
         <v>39927</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>44</v>
+      <c r="B68" s="48">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>44</v>
@@ -14179,8 +14252,9 @@
       <c r="A69" s="10">
         <v>39947</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>44</v>
+      <c r="B69" s="48">
+        <f t="shared" ref="B69:B98" si="1">BL69</f>
+        <v>12</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>44</v>
@@ -14376,8 +14450,9 @@
       <c r="A70" s="25">
         <v>39969</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>44</v>
+      <c r="B70" s="48">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>44</v>
@@ -14573,8 +14648,9 @@
       <c r="A71" s="10">
         <v>40007</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>44</v>
+      <c r="B71" s="48">
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>44</v>
@@ -14770,8 +14846,9 @@
       <c r="A72" s="10">
         <v>40035</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>44</v>
+      <c r="B72" s="48">
+        <f t="shared" si="1"/>
+        <v>10.75</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>44</v>
@@ -14967,8 +15044,9 @@
       <c r="A73" s="10">
         <v>40071</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>44</v>
+      <c r="B73" s="48">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>44</v>
@@ -15164,8 +15242,9 @@
       <c r="A74" s="10">
         <v>40086</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>44</v>
+      <c r="B74" s="48">
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>44</v>
@@ -15361,8 +15440,9 @@
       <c r="A75" s="10">
         <v>40116</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>44</v>
+      <c r="B75" s="48">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>44</v>
@@ -15558,8 +15638,9 @@
       <c r="A76" s="10">
         <v>40142</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>44</v>
+      <c r="B76" s="48">
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>44</v>
@@ -15755,8 +15836,9 @@
       <c r="A77" s="10">
         <v>40175</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>44</v>
+      <c r="B77" s="48">
+        <f t="shared" si="1"/>
+        <v>8.75</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>44</v>
@@ -15952,8 +16034,9 @@
       <c r="A78" s="10">
         <v>40233</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>44</v>
+      <c r="B78" s="48">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>44</v>
@@ -16149,8 +16232,9 @@
       <c r="A79" s="25">
         <v>40266</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>44</v>
+      <c r="B79" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>44</v>
@@ -16346,8 +16430,9 @@
       <c r="A80" s="25">
         <v>40298</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>44</v>
+      <c r="B80" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>44</v>
@@ -16539,12 +16624,13 @@
         <v>92</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>40330</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>44</v>
+      <c r="B81" s="48">
+        <f t="shared" si="1"/>
+        <v>7.75</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>44</v>
@@ -16736,12 +16822,13 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>40539</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>44</v>
+      <c r="B82" s="48">
+        <f t="shared" si="1"/>
+        <v>7.75</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>44</v>
@@ -16933,12 +17020,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>40602</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>44</v>
+      <c r="B83" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>44</v>
@@ -17130,12 +17218,13 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>40666</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>44</v>
+      <c r="B84" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>44</v>
@@ -17327,12 +17416,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>40694</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>44</v>
+      <c r="B85" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>44</v>
@@ -17524,12 +17614,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A86" s="25">
         <v>40784</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>44</v>
+      <c r="B86" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>44</v>
@@ -17721,12 +17812,13 @@
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>40801</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>44</v>
+      <c r="B87" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>44</v>
@@ -17918,12 +18010,13 @@
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A88" s="25">
         <v>40848</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>44</v>
+      <c r="B88" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>44</v>
@@ -18115,12 +18208,13 @@
         <v>140</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>40903</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>44</v>
+      <c r="B89" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>44</v>
@@ -18312,12 +18406,13 @@
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A90" s="25">
         <v>41001</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>44</v>
+      <c r="B90" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>44</v>
@@ -18509,12 +18604,13 @@
         <v>141</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A91" s="25">
         <v>41009</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>44</v>
+      <c r="B91" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>44</v>
@@ -18705,13 +18801,15 @@
       <c r="BM91" s="6" t="s">
         <v>104</v>
       </c>
+      <c r="BN91" s="5"/>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A92" s="25">
         <v>41078</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>44</v>
+      <c r="B92" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>44</v>
@@ -18902,13 +19000,15 @@
       <c r="BM92" s="16" t="s">
         <v>105</v>
       </c>
+      <c r="BN92" s="5"/>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A93" s="25">
         <v>41091</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>44</v>
+      <c r="B93" s="48">
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>44</v>
@@ -19099,13 +19199,15 @@
       <c r="BM93" s="6" t="s">
         <v>106</v>
       </c>
+      <c r="BN93" s="5"/>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>41166</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>44</v>
+      <c r="B94" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>44</v>
@@ -19296,13 +19398,15 @@
       <c r="BM94" s="6" t="s">
         <v>107</v>
       </c>
+      <c r="BN94" s="5"/>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>41254</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>44</v>
+      <c r="B95" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>44</v>
@@ -19493,13 +19597,15 @@
       <c r="BM95" s="6" t="s">
         <v>108</v>
       </c>
+      <c r="BN95" s="5"/>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>41367</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>44</v>
+      <c r="B96" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>44</v>
@@ -19690,13 +19796,15 @@
       <c r="BM96" s="6" t="s">
         <v>109</v>
       </c>
+      <c r="BN96" s="5"/>
     </row>
-    <row r="97" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>41410</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>44</v>
+      <c r="B97" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>44</v>
@@ -19887,13 +19995,15 @@
       <c r="BM97" s="6" t="s">
         <v>110</v>
       </c>
+      <c r="BN97" s="5"/>
     </row>
-    <row r="98" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>41436</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>44</v>
+      <c r="B98" s="48">
+        <f t="shared" si="1"/>
+        <v>8.25</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>44</v>
@@ -20084,13 +20194,15 @@
       <c r="BM98" s="6" t="s">
         <v>111</v>
       </c>
+      <c r="BN98" s="5"/>
     </row>
-    <row r="99" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A99" s="25">
         <v>41470</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>44</v>
+      <c r="B99" s="48">
+        <f>BL99</f>
+        <v>8.25</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>44</v>
@@ -20281,8 +20393,9 @@
       <c r="BM99" s="6" t="s">
         <v>126</v>
       </c>
+      <c r="BN99" s="5"/>
     </row>
-    <row r="100" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A100" s="25">
         <v>41533</v>
       </c>
@@ -20478,8 +20591,9 @@
       <c r="BM100" s="6" t="s">
         <v>125</v>
       </c>
+      <c r="BN100" s="5"/>
     </row>
-    <row r="101" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A101" s="25">
         <v>41673</v>
       </c>
@@ -20487,7 +20601,7 @@
         <v>5.5</v>
       </c>
       <c r="C101" s="5">
-        <f t="shared" ref="C101:C132" si="0">B101-B100</f>
+        <f t="shared" ref="C101:C132" si="2">B101-B100</f>
         <v>0</v>
       </c>
       <c r="D101" s="5">
@@ -20676,8 +20790,9 @@
       <c r="BM101" s="6" t="s">
         <v>112</v>
       </c>
+      <c r="BN101" s="5"/>
     </row>
-    <row r="102" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A102" s="25">
         <v>41687</v>
       </c>
@@ -20685,7 +20800,7 @@
         <v>5.5</v>
       </c>
       <c r="C102" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D102" s="5">
@@ -20874,8 +20989,9 @@
       <c r="BM102" s="6" t="s">
         <v>57</v>
       </c>
+      <c r="BN102" s="5"/>
     </row>
-    <row r="103" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>41701</v>
       </c>
@@ -20883,7 +20999,7 @@
         <v>7</v>
       </c>
       <c r="C103" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
       <c r="D103" s="5">
@@ -21069,8 +21185,9 @@
       <c r="BL103" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN103" s="5"/>
     </row>
-    <row r="104" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A104" s="25">
         <v>41733</v>
       </c>
@@ -21078,7 +21195,7 @@
         <v>7</v>
       </c>
       <c r="C104" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D104" s="5">
@@ -21267,8 +21384,9 @@
       <c r="BM104" s="6" t="s">
         <v>155</v>
       </c>
+      <c r="BN104" s="5"/>
     </row>
-    <row r="105" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>41757</v>
       </c>
@@ -21276,7 +21394,7 @@
         <v>7.5</v>
       </c>
       <c r="C105" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="D105" s="5">
@@ -21462,8 +21580,9 @@
       <c r="BL105" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN105" s="5"/>
     </row>
-    <row r="106" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A106" s="25">
         <v>41820</v>
       </c>
@@ -21471,7 +21590,7 @@
         <v>7.5</v>
       </c>
       <c r="C106" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D106" s="5">
@@ -21660,8 +21779,9 @@
       <c r="BM106" s="6" t="s">
         <v>113</v>
       </c>
+      <c r="BN106" s="5"/>
     </row>
-    <row r="107" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A107" s="25">
         <v>41848</v>
       </c>
@@ -21669,7 +21789,7 @@
         <v>8</v>
       </c>
       <c r="C107" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="D107" s="5">
@@ -21858,8 +21978,9 @@
       <c r="BM107" s="6" t="s">
         <v>166</v>
       </c>
+      <c r="BN107" s="5"/>
     </row>
-    <row r="108" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A108" s="25">
         <v>41928</v>
       </c>
@@ -21867,7 +21988,7 @@
         <v>8</v>
       </c>
       <c r="C108" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D108" s="5">
@@ -22056,8 +22177,9 @@
       <c r="BM108" s="6" t="s">
         <v>124</v>
       </c>
+      <c r="BN108" s="5"/>
     </row>
-    <row r="109" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>41948</v>
       </c>
@@ -22065,7 +22187,7 @@
         <v>9.5</v>
       </c>
       <c r="C109" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
       <c r="D109" s="5">
@@ -22251,8 +22373,9 @@
       <c r="BL109" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN109" s="5"/>
     </row>
-    <row r="110" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A110" s="25">
         <v>41974</v>
       </c>
@@ -22260,7 +22383,7 @@
         <v>9.5</v>
       </c>
       <c r="C110" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D110" s="5">
@@ -22449,8 +22572,9 @@
       <c r="BM110" s="6" t="s">
         <v>51</v>
       </c>
+      <c r="BN110" s="5"/>
     </row>
-    <row r="111" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A111" s="25">
         <v>41984</v>
       </c>
@@ -22458,7 +22582,7 @@
         <v>9.5</v>
       </c>
       <c r="C111" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D111" s="5">
@@ -22647,8 +22771,9 @@
       <c r="BM111" s="6" t="s">
         <v>114</v>
       </c>
+      <c r="BN111" s="5"/>
     </row>
-    <row r="112" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>41985</v>
       </c>
@@ -22656,7 +22781,7 @@
         <v>10.5</v>
       </c>
       <c r="C112" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="D112" s="5">
@@ -22842,8 +22967,9 @@
       <c r="BL112" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN112" s="5"/>
     </row>
-    <row r="113" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>41989</v>
       </c>
@@ -22851,7 +22977,7 @@
         <v>17</v>
       </c>
       <c r="C113" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.5</v>
       </c>
       <c r="D113" s="5">
@@ -23037,8 +23163,9 @@
       <c r="BL113" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN113" s="5"/>
     </row>
-    <row r="114" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A114" s="25">
         <v>41992</v>
       </c>
@@ -23046,7 +23173,7 @@
         <v>17</v>
       </c>
       <c r="C114" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D114" s="5">
@@ -23235,8 +23362,9 @@
       <c r="BM114" s="6" t="s">
         <v>123</v>
       </c>
+      <c r="BN114" s="5"/>
     </row>
-    <row r="115" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A115" s="10">
         <v>42037</v>
       </c>
@@ -23244,7 +23372,7 @@
         <v>15</v>
       </c>
       <c r="C115" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
       <c r="D115" s="5">
@@ -23430,8 +23558,9 @@
       <c r="BL115" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN115" s="5"/>
     </row>
-    <row r="116" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A116" s="10">
         <v>42079</v>
       </c>
@@ -23439,7 +23568,7 @@
         <v>14</v>
       </c>
       <c r="C116" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="D116" s="5">
@@ -23625,8 +23754,9 @@
       <c r="BL116" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN116" s="5"/>
     </row>
-    <row r="117" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A117" s="10">
         <v>42129</v>
       </c>
@@ -23634,7 +23764,7 @@
         <v>12.5</v>
       </c>
       <c r="C117" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1.5</v>
       </c>
       <c r="D117" s="5">
@@ -23820,8 +23950,9 @@
       <c r="BL117" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN117" s="5"/>
     </row>
-    <row r="118" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A118" s="10">
         <v>42171</v>
       </c>
@@ -23829,7 +23960,7 @@
         <v>11.5</v>
       </c>
       <c r="C118" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="D118" s="5">
@@ -24015,8 +24146,9 @@
       <c r="BL118" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN118" s="5"/>
     </row>
-    <row r="119" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A119" s="10">
         <v>42219</v>
       </c>
@@ -24024,7 +24156,7 @@
         <v>11</v>
       </c>
       <c r="C119" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D119" s="5">
@@ -24210,8 +24342,9 @@
       <c r="BL119" s="5">
         <v>8.25</v>
       </c>
+      <c r="BN119" s="5"/>
     </row>
-    <row r="120" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A120" s="25">
         <v>42370</v>
       </c>
@@ -24219,7 +24352,7 @@
         <v>11</v>
       </c>
       <c r="C120" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D120" s="5">
@@ -24408,8 +24541,9 @@
       <c r="BM120" s="6" t="s">
         <v>130</v>
       </c>
+      <c r="BN120" s="5"/>
     </row>
-    <row r="121" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A121" s="10">
         <v>42535</v>
       </c>
@@ -24417,7 +24551,7 @@
         <v>10.5</v>
       </c>
       <c r="C121" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D121" s="5">
@@ -24603,8 +24737,9 @@
       <c r="BL121" s="5">
         <v>10.5</v>
       </c>
+      <c r="BN121" s="5"/>
     </row>
-    <row r="122" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A122" s="10">
         <v>42632</v>
       </c>
@@ -24612,7 +24747,7 @@
         <v>10</v>
       </c>
       <c r="C122" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D122" s="5">
@@ -24798,8 +24933,9 @@
       <c r="BL122" s="5">
         <v>10</v>
       </c>
+      <c r="BN122" s="5"/>
     </row>
-    <row r="123" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A123" s="25">
         <v>42727</v>
       </c>
@@ -24807,7 +24943,7 @@
         <v>10</v>
       </c>
       <c r="C123" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D123" s="5">
@@ -24996,8 +25132,9 @@
       <c r="BM123" s="6" t="s">
         <v>150</v>
       </c>
+      <c r="BN123" s="5"/>
     </row>
-    <row r="124" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A124" s="10">
         <v>42821</v>
       </c>
@@ -25005,7 +25142,7 @@
         <v>9.75</v>
       </c>
       <c r="C124" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="D124" s="5">
@@ -25191,8 +25328,9 @@
       <c r="BL124" s="5">
         <v>9.75</v>
       </c>
+      <c r="BN124" s="5"/>
     </row>
-    <row r="125" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A125" s="10">
         <v>42857</v>
       </c>
@@ -25200,7 +25338,7 @@
         <v>9.25</v>
       </c>
       <c r="C125" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D125" s="5">
@@ -25386,8 +25524,9 @@
       <c r="BL125" s="5">
         <v>9.25</v>
       </c>
+      <c r="BN125" s="5"/>
     </row>
-    <row r="126" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A126" s="10">
         <v>42905</v>
       </c>
@@ -25395,7 +25534,7 @@
         <v>9</v>
       </c>
       <c r="C126" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="D126" s="5">
@@ -25581,8 +25720,9 @@
       <c r="BL126" s="5">
         <v>9</v>
       </c>
+      <c r="BN126" s="5"/>
     </row>
-    <row r="127" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A127" s="25">
         <v>42932</v>
       </c>
@@ -25590,7 +25730,7 @@
         <v>9</v>
       </c>
       <c r="C127" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D127" s="5">
@@ -25779,8 +25919,9 @@
       <c r="BM127" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="BN127" s="5"/>
     </row>
-    <row r="128" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A128" s="10">
         <v>42996</v>
       </c>
@@ -25788,7 +25929,7 @@
         <v>8.5</v>
       </c>
       <c r="C128" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D128" s="5">
@@ -25983,7 +26124,7 @@
         <v>8.25</v>
       </c>
       <c r="C129" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="D129" s="5">
@@ -26178,7 +26319,7 @@
         <v>7.75</v>
       </c>
       <c r="C130" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.5</v>
       </c>
       <c r="D130" s="5">
@@ -26373,7 +26514,7 @@
         <v>7.5</v>
       </c>
       <c r="C131" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="D131" s="5">
@@ -26568,7 +26709,7 @@
         <v>7.25</v>
       </c>
       <c r="C132" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="D132" s="5">
@@ -26763,7 +26904,7 @@
         <v>7.5</v>
       </c>
       <c r="C133" s="5">
-        <f t="shared" ref="C133:C164" si="1">B133-B132</f>
+        <f t="shared" ref="C133:C164" si="3">B133-B132</f>
         <v>0.25</v>
       </c>
       <c r="D133" s="18">
@@ -26959,7 +27100,7 @@
         <v>7.75</v>
       </c>
       <c r="C134" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="D134" s="18">
@@ -27155,7 +27296,7 @@
         <v>7.75</v>
       </c>
       <c r="C135" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D135" s="18">
@@ -27353,7 +27494,7 @@
         <v>7.5</v>
       </c>
       <c r="C136" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="D136" s="18">
@@ -27549,7 +27690,7 @@
         <v>7.25</v>
       </c>
       <c r="C137" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="D137" s="5">
@@ -27747,7 +27888,7 @@
         <v>7</v>
       </c>
       <c r="C138" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="D138" s="5">
@@ -27942,7 +28083,7 @@
         <v>6.5</v>
       </c>
       <c r="C139" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.5</v>
       </c>
       <c r="D139" s="5">
@@ -28137,7 +28278,7 @@
         <v>6.25</v>
       </c>
       <c r="C140" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="D140" s="5">
@@ -28332,7 +28473,7 @@
         <v>6</v>
       </c>
       <c r="C141" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="D141" s="5">
@@ -28527,7 +28668,7 @@
         <v>5.5</v>
       </c>
       <c r="C142" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.5</v>
       </c>
       <c r="D142" s="5">
@@ -28722,7 +28863,7 @@
         <v>5.5</v>
       </c>
       <c r="C143" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D143" s="5">
@@ -28920,7 +29061,7 @@
         <v>4.5</v>
       </c>
       <c r="C144" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="D144" s="5">
@@ -29115,7 +29256,7 @@
         <v>4.25</v>
       </c>
       <c r="C145" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.25</v>
       </c>
       <c r="D145" s="5">
@@ -29310,7 +29451,7 @@
         <v>4.5</v>
       </c>
       <c r="C146" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="D146" s="5">
@@ -29505,7 +29646,7 @@
         <v>5</v>
       </c>
       <c r="C147" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="D147" s="5">
@@ -29700,7 +29841,7 @@
         <v>5.5</v>
       </c>
       <c r="C148" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
       <c r="D148" s="5">
@@ -29895,7 +30036,7 @@
         <v>6.5</v>
       </c>
       <c r="C149" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D149" s="5">
@@ -30090,7 +30231,7 @@
         <v>6.75</v>
       </c>
       <c r="C150" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
       <c r="D150" s="5">
@@ -30285,7 +30426,7 @@
         <v>7.5</v>
       </c>
       <c r="C151" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
       <c r="D151" s="5">
@@ -30480,7 +30621,7 @@
         <v>8.5</v>
       </c>
       <c r="C152" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D152" s="5">
@@ -30675,7 +30816,7 @@
         <v>8.5</v>
       </c>
       <c r="C153" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D153" s="5">
@@ -30873,7 +31014,7 @@
         <v>9.5</v>
       </c>
       <c r="C154" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D154" s="5">
@@ -31068,7 +31209,7 @@
         <v>20</v>
       </c>
       <c r="C155" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10.5</v>
       </c>
       <c r="D155" s="5">
@@ -31263,7 +31404,7 @@
         <v>20</v>
       </c>
       <c r="C156" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D156" s="5">
@@ -31461,7 +31602,7 @@
         <v>20</v>
       </c>
       <c r="C157" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D157" s="5">
@@ -31659,7 +31800,7 @@
         <v>17</v>
       </c>
       <c r="C158" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-3</v>
       </c>
       <c r="D158" s="5">
@@ -31854,7 +31995,7 @@
         <v>14</v>
       </c>
       <c r="C159" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-3</v>
       </c>
       <c r="D159" s="5">
@@ -32049,7 +32190,7 @@
         <v>11</v>
       </c>
       <c r="C160" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-3</v>
       </c>
       <c r="D160" s="5">
@@ -32244,7 +32385,7 @@
         <v>9.5</v>
       </c>
       <c r="C161" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.5</v>
       </c>
       <c r="D161" s="5">
@@ -32439,7 +32580,7 @@
         <v>8</v>
       </c>
       <c r="C162" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-1.5</v>
       </c>
       <c r="D162" s="5">
@@ -32634,7 +32775,7 @@
         <v>7.5</v>
       </c>
       <c r="C163" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.5</v>
       </c>
       <c r="D163" s="5">
@@ -32829,7 +32970,7 @@
         <v>8.5</v>
       </c>
       <c r="C164" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="D164" s="5">
@@ -33024,7 +33165,7 @@
         <v>12</v>
       </c>
       <c r="C165" s="5">
-        <f t="shared" ref="C165:C173" si="2">B165-B164</f>
+        <f t="shared" ref="C165:C173" si="4">B165-B164</f>
         <v>3.5</v>
       </c>
       <c r="D165" s="5">
@@ -33219,7 +33360,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D166" s="5">
@@ -33414,7 +33555,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D167" s="5">
@@ -33612,7 +33753,7 @@
         <v>15</v>
       </c>
       <c r="C168" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="D168" s="5">
@@ -33807,7 +33948,7 @@
         <v>16</v>
       </c>
       <c r="C169" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D169" s="5">
@@ -34002,7 +34143,7 @@
         <v>18</v>
       </c>
       <c r="C170" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="D170" s="5">
@@ -34197,7 +34338,7 @@
         <v>19</v>
       </c>
       <c r="C171" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="D171" s="34">
@@ -34392,7 +34533,7 @@
         <v>21</v>
       </c>
       <c r="C172" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="D172" s="34">
@@ -34587,7 +34728,7 @@
         <v>20</v>
       </c>
       <c r="C173" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>-1</v>
       </c>
       <c r="D173" s="34">
@@ -34782,7 +34923,7 @@
         <v>18</v>
       </c>
       <c r="C174" s="5">
-        <f t="shared" ref="C174" si="3">B174-B173</f>
+        <f t="shared" ref="C174" si="5">B174-B173</f>
         <v>-2</v>
       </c>
       <c r="D174" s="34">
@@ -34977,7 +35118,7 @@
         <v>17</v>
       </c>
       <c r="C175" s="5">
-        <f t="shared" ref="C175:C176" si="4">B175-B174</f>
+        <f t="shared" ref="C175:C176" si="6">B175-B174</f>
         <v>-1</v>
       </c>
       <c r="D175" s="34">
@@ -35172,7 +35313,7 @@
         <v>16.5</v>
       </c>
       <c r="C176" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-0.5</v>
       </c>
       <c r="D176" s="34">
@@ -35461,6 +35602,14 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:N3"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="T3:W3"/>
+    <mergeCell ref="X3:AD3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="BM3:BM4"/>
     <mergeCell ref="BI3:BJ3"/>
     <mergeCell ref="BK3:BK4"/>
@@ -35471,14 +35620,6 @@
     <mergeCell ref="AS3:AY3"/>
     <mergeCell ref="BD3:BH3"/>
     <mergeCell ref="AH3:AL3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="D3:N3"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="T3:W3"/>
-    <mergeCell ref="X3:AD3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
